--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484157_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484157_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6521</v>
+        <v>5.1149</v>
       </c>
       <c r="E2" t="n">
-        <v>1.3356</v>
+        <v>1.602</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3165</v>
+        <v>3.5129</v>
       </c>
       <c r="G2" t="n">
         <v>5.4366</v>
@@ -610,13 +610,13 @@
         <v>2.3806</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.963</v>
+        <v>-0.5002</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3797</v>
+        <v>-0.1133</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5833</v>
+        <v>-0.3869</v>
       </c>
       <c r="V2" t="n">
         <v>-1.0118</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4455</v>
+        <v>3.5587</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1627</v>
+        <v>-0.1797</v>
       </c>
       <c r="F3" t="n">
-        <v>4.6081</v>
+        <v>3.7384</v>
       </c>
       <c r="G3" t="n">
         <v>1.2153</v>
@@ -688,13 +688,13 @@
         <v>2.3806</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1545</v>
+        <v>0.2678</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2606</v>
+        <v>-0.2776</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4151</v>
+        <v>0.5454</v>
       </c>
       <c r="V3" t="n">
         <v>2.0757</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. ESONO MBA</t>
+          <t>L. MARTÍN LLAVERÍA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5596</v>
+        <v>1.3226</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.3308</v>
+        <v>0.8107</v>
       </c>
       <c r="F4" t="n">
-        <v>3.8903</v>
+        <v>0.5119</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3166</v>
+        <v>2.2821</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4478</v>
+        <v>0.8971</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7645</v>
+        <v>1.385</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.2795</v>
+        <v>1.281</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.4803</v>
+        <v>-0.6091</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2008</v>
+        <v>1.8901</v>
       </c>
       <c r="M4" t="n">
-        <v>1.5962</v>
+        <v>1.001</v>
       </c>
       <c r="N4" t="n">
-        <v>1.0325</v>
+        <v>1.5062</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5637</v>
+        <v>-0.5051</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5952</v>
+        <v>0.7935</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.3887</v>
+        <v>-0.3968</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9838</v>
+        <v>1.1903</v>
       </c>
       <c r="S4" t="n">
-        <v>1.9255</v>
+        <v>-0.2806</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3492</v>
+        <v>-0.0736</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5763</v>
+        <v>-0.207</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.2777</v>
+        <v>-1.4724</v>
       </c>
       <c r="W4" t="n">
-        <v>-1.0118</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.266</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9196</v>
+        <v>1.1339</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0735</v>
+        <v>0.0285</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9931</v>
+        <v>1.1053</v>
       </c>
       <c r="G5" t="n">
         <v>0.046</v>
@@ -844,13 +844,13 @@
         <v>0.9919</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3843</v>
+        <v>-0.17</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5611</v>
+        <v>-0.4591</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1768</v>
+        <v>0.289</v>
       </c>
       <c r="V5" t="n">
         <v>0.266</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. MARTÍN LLAVERÍA</t>
+          <t>P. MORENO MARTIN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6113</v>
+        <v>0.9292</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3799</v>
+        <v>0.5448</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2314</v>
+        <v>0.3844</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2821</v>
+        <v>2.5571</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8971</v>
+        <v>3.2605</v>
       </c>
       <c r="I6" t="n">
-        <v>1.385</v>
+        <v>-0.7034</v>
       </c>
       <c r="J6" t="n">
-        <v>1.281</v>
+        <v>1.4969</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6091</v>
+        <v>2.0968</v>
       </c>
       <c r="L6" t="n">
-        <v>1.8901</v>
+        <v>-0.5999</v>
       </c>
       <c r="M6" t="n">
-        <v>1.001</v>
+        <v>1.0601</v>
       </c>
       <c r="N6" t="n">
-        <v>1.5062</v>
+        <v>1.1637</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5051</v>
+        <v>-0.1035</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7935</v>
+        <v>1.5871</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.3968</v>
+        <v>-0.1984</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1903</v>
+        <v>1.7855</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9919</v>
+        <v>-0.802</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5044</v>
+        <v>-0.7538</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4876</v>
+        <v>-0.0483</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.4724</v>
+        <v>-2.4129</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.4724</v>
+        <v>-2.4129</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2619</v>
+        <v>0.6442</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.8265</v>
+        <v>-2.1917</v>
       </c>
       <c r="F7" t="n">
-        <v>3.0884</v>
+        <v>2.8359</v>
       </c>
       <c r="G7" t="n">
         <v>0.1922</v>
@@ -1000,13 +1000,13 @@
         <v>1.5871</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5255</v>
+        <v>-0.1431</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1222</v>
+        <v>-0.4874</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5968</v>
+        <v>0.3443</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. MORENO MARTIN</t>
+          <t>J. SERRA ANGLÈS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0066</v>
+        <v>0.4754</v>
       </c>
       <c r="E8" t="n">
-        <v>0.114</v>
+        <v>-1.3439</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1206</v>
+        <v>1.8193</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5571</v>
+        <v>1.0663</v>
       </c>
       <c r="H8" t="n">
-        <v>3.2605</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7034</v>
+        <v>0.9755</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4969</v>
+        <v>1.3796</v>
       </c>
       <c r="K8" t="n">
-        <v>2.0968</v>
+        <v>-0.3926</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5999</v>
+        <v>1.7722</v>
       </c>
       <c r="M8" t="n">
-        <v>1.0601</v>
+        <v>-0.3133</v>
       </c>
       <c r="N8" t="n">
-        <v>1.1637</v>
+        <v>0.4835</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1035</v>
+        <v>-0.7967</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5871</v>
+        <v>0.3968</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1984</v>
+        <v>-1.9838</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7855</v>
+        <v>2.3806</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.7378</v>
+        <v>-0.6504</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.1846</v>
+        <v>-0.4024</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5533</v>
+        <v>-0.248</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.4129</v>
+        <v>-0.3373</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.3373</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.4129</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. SERRA ANGLÈS</t>
+          <t>I. VILLAR CANTERO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1976</v>
+        <v>0.189</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8767</v>
+        <v>-1.2002</v>
       </c>
       <c r="F9" t="n">
-        <v>1.679</v>
+        <v>1.3892</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0663</v>
+        <v>-0.479</v>
       </c>
       <c r="H9" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.8981</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9755</v>
+        <v>-1.3771</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3796</v>
+        <v>-0.5278</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3926</v>
+        <v>0.0721</v>
       </c>
       <c r="L9" t="n">
-        <v>1.7722</v>
+        <v>-0.5999</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3133</v>
+        <v>0.0488</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4835</v>
+        <v>0.826</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7967</v>
+        <v>-0.7772</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3968</v>
+        <v>0.1984</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9838</v>
+        <v>-1.3887</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3806</v>
+        <v>1.5871</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3235</v>
+        <v>-0.3996</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9352</v>
+        <v>-0.153</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3883</v>
+        <v>-0.2467</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3373</v>
+        <v>0.8692</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3373</v>
+        <v>0.8692</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. VILLAR CANTERO</t>
+          <t>J. ESONO MBA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3183</v>
+        <v>0.1513</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4269</v>
+        <v>-3.4304</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1086</v>
+        <v>3.5817</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.479</v>
+        <v>0.3166</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8981</v>
+        <v>-0.4478</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.3771</v>
+        <v>0.7645</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5278</v>
+        <v>-1.2795</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0721</v>
+        <v>-1.4803</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5999</v>
+        <v>0.2008</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0488</v>
+        <v>1.5962</v>
       </c>
       <c r="N10" t="n">
-        <v>0.826</v>
+        <v>1.0325</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7772</v>
+        <v>0.5637</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1984</v>
+        <v>0.5952</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.3887</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5871</v>
+        <v>1.9838</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9069</v>
+        <v>0.5172</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3797</v>
+        <v>0.2495</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5272</v>
+        <v>0.2677</v>
       </c>
       <c r="V10" t="n">
-        <v>0.8692</v>
+        <v>-1.2777</v>
       </c>
       <c r="W10" t="n">
-        <v>0.8692</v>
+        <v>-1.0118</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B. BONET TORRALBA</t>
+          <t>M. GARCIA IBAÑEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.5562</v>
+        <v>-1.5538</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.4985</v>
+        <v>-3.1398</v>
       </c>
       <c r="F11" t="n">
-        <v>3.9423</v>
+        <v>1.586</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.7544</v>
+        <v>-2.798</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.0781</v>
+        <v>-1.2498</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6762</v>
+        <v>-1.5482</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.1918</v>
+        <v>-3.0994</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.6321</v>
+        <v>-1.9398</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5597</v>
+        <v>-1.1596</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4374</v>
+        <v>0.3014</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5538999999999999</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1165</v>
+        <v>-0.3886</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1984</v>
+        <v>2.3806</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.9758</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3.1741</v>
+        <v>2.3806</v>
       </c>
       <c r="S11" t="n">
-        <v>1.2658</v>
+        <v>-0.4619</v>
       </c>
       <c r="T11" t="n">
-        <v>0.669</v>
+        <v>-0.5724</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5968</v>
+        <v>0.1105</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.266</v>
+        <v>-0.6745</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.532</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.266</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. GARCIA IBAÑEZ</t>
+          <t>B. BONET TORRALBA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.459</v>
+        <v>-1.8063</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.8766</v>
+        <v>-5.4962</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4176</v>
+        <v>3.6898</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.798</v>
+        <v>-1.7544</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.2498</v>
+        <v>-1.0781</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.5482</v>
+        <v>-0.6762</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.0994</v>
+        <v>-2.1918</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.9398</v>
+        <v>-1.6321</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.1596</v>
+        <v>-0.5597</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3014</v>
+        <v>0.4374</v>
       </c>
       <c r="N12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.5538999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3886</v>
+        <v>-0.1165</v>
       </c>
       <c r="P12" t="n">
-        <v>2.3806</v>
+        <v>0.1984</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-2.9758</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3806</v>
+        <v>3.1741</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3671</v>
+        <v>0.0156</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.3092</v>
+        <v>-0.3286</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0579</v>
+        <v>0.3443</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.6745</v>
+        <v>-0.266</v>
       </c>
       <c r="W12" t="n">
-        <v>0.532</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2065</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="13">
@@ -1423,31 +1423,31 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.9123</v>
+        <v>10.1591</v>
       </c>
       <c r="E13" t="n">
-        <v>-15.2427</v>
+        <v>-13.9959</v>
       </c>
       <c r="F13" t="n">
-        <v>24.1547</v>
+        <v>24.1548</v>
       </c>
       <c r="G13" t="n">
         <v>8.0808</v>
       </c>
       <c r="H13" t="n">
-        <v>5.2951</v>
+        <v>5.295100000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>2.785900000000001</v>
+        <v>2.7859</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8883999999999994</v>
+        <v>0.8883999999999985</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.0055</v>
+        <v>-5.005500000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>5.8942</v>
+        <v>5.894199999999999</v>
       </c>
       <c r="M13" t="n">
         <v>7.192200000000001</v>
@@ -1459,7 +1459,7 @@
         <v>-3.1082</v>
       </c>
       <c r="P13" t="n">
-        <v>8.9274</v>
+        <v>8.927399999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-12.895</v>
@@ -1468,16 +1468,16 @@
         <v>21.8222</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.8542</v>
+        <v>-2.6072</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.6185</v>
+        <v>-3.371700000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7642000000000002</v>
+        <v>0.7642999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>-4.2417</v>
+        <v>-4.241700000000001</v>
       </c>
       <c r="W13" t="n">
         <v>1.382</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.3951</v>
+        <v>2.9154</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3504</v>
+        <v>0.7585</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0447</v>
+        <v>2.1569</v>
       </c>
       <c r="G14" t="n">
         <v>0.0552</v>
@@ -1546,13 +1546,13 @@
         <v>2.3806</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0216</v>
+        <v>0.4988</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3456</v>
+        <v>0.0625</v>
       </c>
       <c r="U14" t="n">
-        <v>0.324</v>
+        <v>0.4363</v>
       </c>
       <c r="V14" t="n">
         <v>3.3534</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9054</v>
+        <v>0.6964</v>
       </c>
       <c r="E15" t="n">
-        <v>-3.8953</v>
+        <v>-4.7115</v>
       </c>
       <c r="F15" t="n">
-        <v>5.8007</v>
+        <v>5.4079</v>
       </c>
       <c r="G15" t="n">
         <v>0.4782</v>
@@ -1624,13 +1624,13 @@
         <v>1.9838</v>
       </c>
       <c r="S15" t="n">
-        <v>2.4588</v>
+        <v>1.2498</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2018</v>
+        <v>0.3856</v>
       </c>
       <c r="U15" t="n">
-        <v>1.257</v>
+        <v>0.8642</v>
       </c>
       <c r="V15" t="n">
         <v>1.349</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0518</v>
+        <v>-0.012</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.5626</v>
+        <v>-1.7666</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6144</v>
+        <v>1.7547</v>
       </c>
       <c r="G16" t="n">
         <v>3.6814</v>
@@ -1702,13 +1702,13 @@
         <v>2.1822</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9494</v>
+        <v>0.8856000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7086</v>
+        <v>0.5046</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2408</v>
+        <v>0.381</v>
       </c>
       <c r="V16" t="n">
         <v>-1.2065</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2312</v>
+        <v>-0.045</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8728</v>
+        <v>-0.7708</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.7258</v>
       </c>
       <c r="G17" t="n">
         <v>0.2455</v>
@@ -1780,13 +1780,13 @@
         <v>0.3968</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4767</v>
+        <v>-0.2905</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4988</v>
+        <v>-0.3967</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0221</v>
+        <v>0.1062</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3068</v>
+        <v>-0.2405</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7654</v>
+        <v>-0.8673999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4586</v>
+        <v>0.6269</v>
       </c>
       <c r="G18" t="n">
         <v>-0.1985</v>
@@ -1858,13 +1858,13 @@
         <v>0.9919</v>
       </c>
       <c r="S18" t="n">
-        <v>0.356</v>
+        <v>0.4223</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2099</v>
+        <v>0.1078</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1461</v>
+        <v>0.3145</v>
       </c>
       <c r="V18" t="n">
         <v>-0.266</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9917</v>
+        <v>-0.5734</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6306</v>
+        <v>-1.3245</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6389</v>
+        <v>0.7511</v>
       </c>
       <c r="G19" t="n">
         <v>-0.9989</v>
@@ -1936,13 +1936,13 @@
         <v>0.9919</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5203</v>
+        <v>-0.102</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8728</v>
+        <v>-0.5667</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3525</v>
+        <v>0.4647</v>
       </c>
       <c r="V19" t="n">
         <v>-0.266</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5356</v>
+        <v>-2.0126</v>
       </c>
       <c r="E20" t="n">
         <v>-4.3012</v>
       </c>
       <c r="F20" t="n">
-        <v>2.7656</v>
+        <v>2.2887</v>
       </c>
       <c r="G20" t="n">
         <v>-1.5483</v>
@@ -2014,13 +2014,13 @@
         <v>1.7855</v>
       </c>
       <c r="S20" t="n">
-        <v>1.7225</v>
+        <v>1.2455</v>
       </c>
       <c r="T20" t="n">
         <v>0.0738</v>
       </c>
       <c r="U20" t="n">
-        <v>1.6486</v>
+        <v>1.1717</v>
       </c>
       <c r="V20" t="n">
         <v>0.8692</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6296</v>
+        <v>-2.7137</v>
       </c>
       <c r="E21" t="n">
         <v>-3.1622</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5327</v>
+        <v>0.4485</v>
       </c>
       <c r="G21" t="n">
         <v>-3.8941</v>
@@ -2092,13 +2092,13 @@
         <v>1.1903</v>
       </c>
       <c r="S21" t="n">
-        <v>0.59</v>
+        <v>0.5059</v>
       </c>
       <c r="T21" t="n">
         <v>-0.1926</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7827</v>
+        <v>0.6985</v>
       </c>
       <c r="V21" t="n">
         <v>0.6745</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.5695</v>
+        <v>-6.9267</v>
       </c>
       <c r="E22" t="n">
-        <v>-8.315099999999999</v>
+        <v>-8.009</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7456</v>
+        <v>1.0823</v>
       </c>
       <c r="G22" t="n">
         <v>-5.9012</v>
@@ -2170,13 +2170,13 @@
         <v>0.9919</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2039</v>
+        <v>-0.5611</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0485</v>
+        <v>-0.7423999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1554</v>
+        <v>0.1813</v>
       </c>
       <c r="V22" t="n">
         <v>-0.266</v>
@@ -2206,7 +2206,7 @@
         <v>-8.912100000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-24.1548</v>
+        <v>-24.1547</v>
       </c>
       <c r="F23" t="n">
         <v>15.2428</v>
@@ -2248,10 +2248,10 @@
         <v>12.8949</v>
       </c>
       <c r="S23" t="n">
-        <v>3.854200000000001</v>
+        <v>3.8543</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7642000000000002</v>
+        <v>-0.7640999999999999</v>
       </c>
       <c r="U23" t="n">
         <v>4.6184</v>
